--- a/docs/qa/upload-templates/capacity_calendar_upload_template.xlsx
+++ b/docs/qa/upload-templates/capacity_calendar_upload_template.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,16 @@
           <t>available_hours</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>overtime_hours</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,6 +493,10 @@
       <c r="D2" t="n">
         <v>8</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,6 +517,14 @@
       <c r="D3" t="n">
         <v>8</v>
       </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Peak load OT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +545,10 @@
       <c r="D4" t="n">
         <v>8</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
